--- a/d/2026-09-05_会员有效性分析.xlsx
+++ b/d/2026-09-05_会员有效性分析.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C3" t="n">
         <v>608</v>
       </c>
       <c r="D3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>94.41</v>
+        <v>94.26000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>5.59</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="4">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C5" t="n">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -709,16 +709,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" t="n">
         <v>26</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
+        <v>36.59</v>
       </c>
     </row>
     <row r="4">
@@ -1753,19 +1753,19 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>APR成都北城天街</t>
+          <t>华为厦门思明瑞景广场</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>四川新跃</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E42" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -1780,19 +1780,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>华为厦门思明瑞景广场</t>
+          <t>APR成都北城天街</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>福建易联</t>
+          <t>四川新跃</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
         <v>34</v>
@@ -5427,7 +5427,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>178****8955</t>
+          <t>135****1932</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>华为北京东坝万达</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>135****1932</t>
+          <t>178****8955</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>华为北京东坝万达</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5473,7 +5473,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>138****9886</t>
+          <t>185****7000</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京丰科万达</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>185****7000</t>
+          <t>138****9886</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5519,7 +5519,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>136****4066</t>
+          <t>150****2535</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>华为北京清河万象汇</t>
+          <t>华为北京通州万达</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>150****2535</t>
+          <t>136****4066</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>华为北京通州万达</t>
+          <t>华为北京清河万象汇</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5654,7 +5654,7 @@
         <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -5669,7 +5669,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
@@ -5706,7 +5706,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5">
@@ -5732,7 +5732,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6">
@@ -5758,7 +5758,7 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -5810,7 +5810,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9">
@@ -5836,7 +5836,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
@@ -5862,7 +5862,7 @@
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -5940,7 +5940,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -5966,7 +5966,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6044,7 +6044,7 @@
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18">
@@ -6148,7 +6148,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22">
@@ -6174,7 +6174,7 @@
         <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23">
@@ -6200,7 +6200,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24">
@@ -6226,7 +6226,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25">
@@ -6252,7 +6252,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
@@ -6278,7 +6278,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
@@ -6304,7 +6304,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28">
@@ -6330,7 +6330,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
@@ -6356,7 +6356,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
@@ -6382,7 +6382,7 @@
         <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
@@ -6408,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32">
@@ -6434,7 +6434,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33">
@@ -6460,7 +6460,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
@@ -6486,7 +6486,7 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35">
@@ -6512,7 +6512,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36">
@@ -6538,7 +6538,7 @@
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37">
@@ -6564,7 +6564,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38">
@@ -6590,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39">
@@ -6616,7 +6616,7 @@
         <v>1</v>
       </c>
       <c r="F39" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40">
@@ -6642,7 +6642,7 @@
         <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41">
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42">
@@ -6694,7 +6694,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -6750,7 +6750,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
         <v>34</v>
@@ -6782,7 +6782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:G161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7246,7 +7246,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -7281,7 +7281,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -7316,7 +7316,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -7666,7 +7666,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -7876,7 +7876,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -8401,7 +8401,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -8996,7 +8996,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -9731,7 +9731,7 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -9801,7 +9801,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -9836,7 +9836,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -9976,7 +9976,7 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -10676,7 +10676,7 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -11222,12 +11222,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>DJI上海静安大悦城授权体验店</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LSD2026090501123868</t>
+          <t>LSD2026090501125273</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -11236,7 +11236,7 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -11252,17 +11252,17 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>北京飞航</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DJI北京东方新天地授权体验店</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LSD2026090501120604</t>
+          <t>LSD2026090501123868</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -11271,7 +11271,7 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LSD2026090501121632</t>
+          <t>LSD2026090501120604</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -11327,12 +11327,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DJI北京中关村大融城授权体验店</t>
+          <t>DJI北京东方新天地授权体验店</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LSD2026090501119861</t>
+          <t>LSD2026090501121632</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -11341,7 +11341,7 @@
         </is>
       </c>
       <c r="F133" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -11362,12 +11362,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DJI北京王府井APM授权高级体验店</t>
+          <t>DJI北京中关村大融城授权体验店</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LSD2026090501119258</t>
+          <t>LSD2026090501119861</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -11376,7 +11376,7 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -11402,7 +11402,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LSD2026090501119279</t>
+          <t>LSD2026090501119258</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -11411,7 +11411,7 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LSD2026090501119840</t>
+          <t>LSD2026090501119279</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -11446,7 +11446,7 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LSD2026090501119926</t>
+          <t>LSD2026090501119840</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -11481,7 +11481,7 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LSD2026090501119967</t>
+          <t>LSD2026090501119926</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -11516,7 +11516,7 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LSD2026090501121855</t>
+          <t>LSD2026090501119967</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -11551,7 +11551,7 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LSD2026090501122094</t>
+          <t>LSD2026090501121855</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -11586,7 +11586,7 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LSD2026090501123856</t>
+          <t>LSD2026090501122094</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LSD2026090501125114</t>
+          <t>LSD2026090501123856</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DJI北京西单大悦城授权体验店</t>
+          <t>DJI北京王府井APM授权高级体验店</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LSD2026090501122863</t>
+          <t>LSD2026090501125114</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -11691,7 +11691,7 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -11712,12 +11712,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DJI北京西红门荟聚中心授权体验店</t>
+          <t>DJI北京西单大悦城授权体验店</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LSD2026090501124961</t>
+          <t>LSD2026090501122863</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -11726,7 +11726,7 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -11747,12 +11747,12 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DJI北京顺义华联授权体验店</t>
+          <t>DJI北京西红门荟聚中心授权体验店</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LSD2026090501120914</t>
+          <t>LSD2026090501124961</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -11761,7 +11761,7 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LSD2026090501120950</t>
+          <t>LSD2026090501120914</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -11796,7 +11796,7 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -11817,12 +11817,12 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DJI北京首都机场授权体验店</t>
+          <t>DJI北京顺义华联授权体验店</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LSD2026090501122039</t>
+          <t>LSD2026090501120950</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -11852,12 +11852,12 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京大兴机场概念店</t>
+          <t>DJI北京首都机场授权体验店</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LSD2026090501119328</t>
+          <t>LSD2026090501122039</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -11887,12 +11887,12 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DJI大疆哈苏北京芳草地概念店</t>
+          <t>DJI大疆哈苏北京大兴机场概念店</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LSD2026090501123639</t>
+          <t>LSD2026090501119328</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -11901,7 +11901,7 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LSD2026090501124425</t>
+          <t>LSD2026090501123639</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -11936,7 +11936,7 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -11947,31 +11947,36 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>北京易联</t>
+          <t>北京飞航</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>华为北京槐房万达</t>
+          <t>DJI大疆哈苏北京芳草地概念店</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LSD2026090301108322</t>
+          <t>LSD2026090501124425</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>178****8955</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>4</v>
+        <v>136</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -11992,7 +11997,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LSD2026090301108475</t>
+          <t>LSD2026090301108322</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -12022,7 +12027,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LSD2026090301108558</t>
+          <t>LSD2026090301108475</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -12052,7 +12057,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LSD2026090301108836</t>
+          <t>LSD2026090301108558</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -12067,7 +12072,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -12077,21 +12082,21 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>华为北京牡丹园翠微</t>
+          <t>华为北京槐房万达</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LSD2026090401114655</t>
+          <t>LSD2026090301108836</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>183****2985</t>
+          <t>178****8955</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156">
@@ -12112,7 +12117,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LSD2026090401114717</t>
+          <t>LSD2026090401114655</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -12127,7 +12132,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -12142,7 +12147,7 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LSD2026090501119331</t>
+          <t>LSD2026090401114717</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -12157,7 +12162,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -12167,17 +12172,17 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>华为北京丰科万达</t>
+          <t>华为北京牡丹园翠微</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LSD2026090401115084</t>
+          <t>LSD2026090501119331</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>185****7000</t>
+          <t>183****2985</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -12202,7 +12207,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LSD2026090401115104</t>
+          <t>LSD2026090401115084</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -12232,15 +12237,45 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>LSD2026090401115104</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>185****7000</t>
+        </is>
+      </c>
+      <c r="F160" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>华为北京丰科万达</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
           <t>LSD2026090401115173</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>185****7000</t>
         </is>
       </c>
-      <c r="F160" t="n">
+      <c r="F161" t="n">
         <v>3</v>
       </c>
     </row>
@@ -12526,12 +12561,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -12581,12 +12616,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -12691,12 +12726,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -12746,12 +12781,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -12911,12 +12946,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -13131,12 +13166,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -13241,12 +13276,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -13351,12 +13386,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -13461,12 +13496,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -13626,12 +13661,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -13681,12 +13716,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -13901,12 +13936,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -13956,12 +13991,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -14066,12 +14101,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -14121,12 +14156,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -14231,12 +14266,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -14396,12 +14431,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -14506,12 +14541,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -14561,12 +14596,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -14616,12 +14651,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -14671,12 +14706,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -14781,12 +14816,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -14891,12 +14926,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -14946,12 +14981,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -15001,12 +15036,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -15111,12 +15146,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -15166,12 +15201,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K53" t="n">
@@ -15276,12 +15311,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -15331,12 +15366,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -15386,12 +15421,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -15441,12 +15476,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -15551,12 +15586,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K60" t="n">
@@ -15661,12 +15696,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -15716,12 +15751,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -15771,12 +15806,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -15991,12 +16026,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -16156,12 +16191,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -16211,12 +16246,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -16321,12 +16356,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -16376,12 +16411,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -16431,12 +16466,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -16486,12 +16521,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16596,12 +16631,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -16871,12 +16906,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -16926,12 +16961,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -17036,12 +17071,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -17091,12 +17126,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -17201,12 +17236,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -17311,12 +17346,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -17476,12 +17511,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K95" t="n">
@@ -17531,12 +17566,12 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K96" t="n">
@@ -17586,12 +17621,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -17641,12 +17676,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K98" t="n">
@@ -17696,12 +17731,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -17806,12 +17841,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -17916,12 +17951,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -17971,12 +18006,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -18081,12 +18116,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -18136,12 +18171,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -18356,12 +18391,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -18411,12 +18446,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K112" t="n">
@@ -18521,12 +18556,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -18576,12 +18611,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -18631,12 +18666,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -18741,12 +18776,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -18796,12 +18831,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K119" t="n">
@@ -18851,12 +18886,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -18906,12 +18941,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -19016,12 +19051,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -19071,12 +19106,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -19181,12 +19216,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -19291,12 +19326,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -21601,12 +21636,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K170" t="n">
@@ -21876,12 +21911,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -21986,12 +22021,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -22041,12 +22076,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K178" t="n">
@@ -22096,12 +22131,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -22261,12 +22296,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -22426,12 +22461,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K185" t="n">
@@ -22536,12 +22571,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K187" t="n">
@@ -22591,12 +22626,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K188" t="n">
@@ -22646,12 +22681,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K189" t="n">
@@ -22701,12 +22736,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K190" t="n">
@@ -22811,12 +22846,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K192" t="n">
@@ -22921,12 +22956,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K194" t="n">
@@ -23086,12 +23121,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K197" t="n">
@@ -23141,12 +23176,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K198" t="n">
@@ -23196,12 +23231,12 @@
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K199" t="n">
@@ -23251,12 +23286,12 @@
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K200" t="n">
@@ -23361,12 +23396,12 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K202" t="n">
@@ -23416,12 +23451,12 @@
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188275</t>
         </is>
       </c>
       <c r="K203" t="n">
@@ -23471,12 +23506,12 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K204" t="n">
@@ -23526,12 +23561,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K205" t="n">
@@ -23581,12 +23616,12 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+512GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>6942103188275</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K206" t="n">
@@ -23691,12 +23726,12 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K208" t="n">
@@ -23746,12 +23781,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K209" t="n">
@@ -23856,12 +23891,12 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K211" t="n">
@@ -24021,12 +24056,12 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K214" t="n">
@@ -24131,12 +24166,12 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K216" t="n">
@@ -24186,12 +24221,12 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K217" t="n">
@@ -24241,12 +24276,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K218" t="n">
@@ -24296,12 +24331,12 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K219" t="n">
@@ -24351,12 +24386,12 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K220" t="n">
@@ -24406,12 +24441,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K221" t="n">
@@ -24626,12 +24661,12 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>智选 艾优智能剃须刀 尊享款 H1钛金灰 演示样机</t>
+          <t>EasyFit 2 曜石黑 氟橡胶表带 黑 演示样机</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>YJ6970871389662</t>
+          <t>YJ6941487208418</t>
         </is>
       </c>
       <c r="K225" t="n">
@@ -24681,12 +24716,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>EasyFit 2 曜石黑 氟橡胶表带 黑 演示样机</t>
+          <t>智选 艾优智能剃须刀 尊享款 H1钛金灰 演示样机</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>YJ6941487208418</t>
+          <t>YJ6970871389662</t>
         </is>
       </c>
       <c r="K226" t="n">
@@ -24901,12 +24936,12 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188220</t>
         </is>
       </c>
       <c r="K230" t="n">
@@ -25011,12 +25046,12 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188213</t>
         </is>
       </c>
       <c r="K232" t="n">
@@ -25066,12 +25101,12 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K233" t="n">
@@ -25121,12 +25156,12 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K234" t="n">
@@ -25231,12 +25266,12 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>6942103188206</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K236" t="n">
@@ -25286,12 +25321,12 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>6942103188237</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K237" t="n">
@@ -25341,12 +25376,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 晨曦金</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 飞天青</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>6942103188213</t>
+          <t>6942103188206</t>
         </is>
       </c>
       <c r="K238" t="n">
@@ -25451,12 +25486,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 雪域白</t>
+          <t>畅享 90 Pro Max CHZ-AL00 8GB+256GB 曜金黑</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>6942103188220</t>
+          <t>6942103188237</t>
         </is>
       </c>
       <c r="K240" t="n">
@@ -25671,12 +25706,12 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(12GB+512GB) 云杉绿</t>
+          <t>Mate 80 VYG-AL30(12GB+512GB) 晨曦金</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>6942103191640</t>
+          <t>6942103191657</t>
         </is>
       </c>
       <c r="K244" t="n">
@@ -25726,12 +25761,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Mate 80 VYG-AL30(12GB+512GB) 晨曦金</t>
+          <t>Mate 80 VYG-AL30(12GB+512GB) 云杉绿</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>6942103191657</t>
+          <t>6942103191640</t>
         </is>
       </c>
       <c r="K245" t="n">
@@ -26831,12 +26866,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>195****64870</t>
+          <t>195****64757</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -26902,12 +26937,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>195****64757</t>
+          <t>195****64870</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -27115,12 +27150,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M25 折叠旋转 Mac 支架 灰色</t>
+          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6955482541180</t>
+          <t>6946333017596</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -27181,17 +27216,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>鼠标和键盘</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
+          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6970412220850</t>
+          <t>6973620631524</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -27257,12 +27292,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
+          <t>TOMTOC Defender A14 城市简约手提电脑包</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6922329934702</t>
+          <t>6970412220850</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -27323,17 +27358,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
+          <t>VOKAMO沃咔曼 清薄键盘保护膜</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6946333017596</t>
+          <t>6922329934702</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -27394,17 +27429,17 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>鼠标和键盘</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>ZUER卓耳 四向滚轮三模无线鼠标</t>
+          <t>RECCI锐思 RHO-M25 折叠旋转 Mac 支架 灰色</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6973620631524</t>
+          <t>6955482541180</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -27465,17 +27500,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>ZGA 米兰尼斯金属磁吸表带 Watch 38/40/41mm 黑色</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 42mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6927123804657</t>
+          <t>6942297146396</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -27536,17 +27571,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 42mm 保护膜 V3</t>
+          <t>ZGA 米兰尼斯金属磁吸表带 Watch 38/40/41mm 黑色</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6942297146396</t>
+          <t>6927123804657</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -27607,17 +27642,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6955482539514</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -27678,17 +27713,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6922329935587</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -27749,17 +27784,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 雅致黑</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6922329935952</t>
+          <t>6955482539514</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -27820,17 +27855,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17 冰川减震磁吸肤感保护壳 磨砂透黑</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6922329935587</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -27891,17 +27926,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -27962,17 +27997,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>VOKAMO 沃咔曼 iPhone 系列 3D 钻石高清三强钢化玻璃膜 黑 iPhone 17/17 Pro</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6922329935952</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -28033,17 +28068,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -28317,17 +28352,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>6955482533109</t>
+          <t>6927123805548</t>
         </is>
       </c>
       <c r="L26" t="n">
@@ -28459,17 +28494,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6927123805548</t>
+          <t>6955482533109</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -28606,12 +28641,12 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6922329935303</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -28672,17 +28707,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -28814,17 +28849,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6922329935303</t>
         </is>
       </c>
       <c r="L33" t="n">
@@ -29245,12 +29280,12 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -29316,12 +29351,12 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -29458,12 +29493,12 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>6927123810382</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -29671,12 +29706,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 防偷窥防静电二强钢化膜 黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>6927123810382</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -29808,17 +29843,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>FPV</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>DJI Neo 2（仅飞行器）</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>6937224131767</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -29879,17 +29914,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>FPV</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Neo 2（仅飞行器）</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224131767</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -32357,12 +32392,12 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 零度白</t>
+          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 幻夜黑</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>6942103195433</t>
+          <t>6942103195419</t>
         </is>
       </c>
       <c r="L83" t="n">
@@ -32428,12 +32463,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 幻夜黑</t>
+          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 零度白</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>6942103195419</t>
+          <t>6942103195433</t>
         </is>
       </c>
       <c r="L84" t="n">
@@ -33138,12 +33173,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6927123810429</t>
         </is>
       </c>
       <c r="L94" t="n">
@@ -33204,17 +33239,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L95" t="n">
@@ -33280,12 +33315,12 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L96" t="n">
@@ -33351,12 +33386,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L97" t="n">
@@ -33493,12 +33528,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L99" t="n">
@@ -33559,17 +33594,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 黑色 iPhone 17</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>6927123810429</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L100" t="n">
@@ -34061,12 +34096,12 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
+          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>6922329936645</t>
+          <t>6955482530214</t>
         </is>
       </c>
       <c r="L107" t="n">
@@ -34127,17 +34162,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L108" t="n">
@@ -34198,17 +34233,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>4895241136474</t>
         </is>
       </c>
       <c r="L109" t="n">
@@ -34269,17 +34304,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MP26 未来磁吸双向快充移动电源</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>6955482530214</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L110" t="n">
@@ -34340,17 +34375,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L111" t="n">
@@ -34411,17 +34446,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>SWITCHEASYiPhone 系列 LenStand M 镜头支架防摔保护壳珊瑚 iPhone 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>4895241136474</t>
+          <t>6922329936645</t>
         </is>
       </c>
       <c r="L112" t="n">
@@ -34487,12 +34522,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L113" t="n">
@@ -34842,12 +34877,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L118" t="n">
@@ -34908,17 +34943,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -34979,17 +35014,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L120" t="n">
@@ -35055,12 +35090,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L121" t="n">
@@ -35121,17 +35156,17 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -35192,17 +35227,17 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L123" t="n">
@@ -35263,17 +35298,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L124" t="n">
@@ -35334,17 +35369,17 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L125" t="n">
@@ -35410,12 +35445,12 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L126" t="n">
@@ -35552,12 +35587,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482542934</t>
         </is>
       </c>
       <c r="L128" t="n">
@@ -35618,17 +35653,17 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 薄暮灰</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>6938741702959</t>
+          <t>6922329935501</t>
         </is>
       </c>
       <c r="L129" t="n">
@@ -35694,12 +35729,12 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>6927123809867</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L130" t="n">
@@ -35760,17 +35795,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>CLEER可丽尔 ARC 6 开放式 AI 耳机 薄暮灰</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6938741702959</t>
         </is>
       </c>
       <c r="L131" t="n">
@@ -35831,17 +35866,17 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>6955482539477</t>
+          <t>6927123810559</t>
         </is>
       </c>
       <c r="L132" t="n">
@@ -35902,17 +35937,17 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 钛金色</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17 Pro / 17 Pro Max</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>6955482542934</t>
+          <t>6927123809867</t>
         </is>
       </c>
       <c r="L133" t="n">
@@ -35973,17 +36008,17 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L134" t="n">
@@ -36044,17 +36079,17 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L135" t="n">
@@ -36115,17 +36150,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 橙色 iPhone 17 Pro Max</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>6927123810559</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L136" t="n">
@@ -36191,12 +36226,12 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线</t>
+          <t>MAXCO美能格 MW17 五合一无线充蓝牙音箱 霜露白</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>6922329935501</t>
+          <t>6955482539477</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -36328,17 +36363,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
+          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>XMPZ202612189</t>
+          <t>195****28869</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -36399,17 +36434,17 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 256GB 银色 - MG8T4CH/A</t>
+          <t>MAGICPIX魔图极秀 iPhone 17 系列摄影课程 - 用 iPhone 拍照片</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>195****28869</t>
+          <t>XMPZ202612189</t>
         </is>
       </c>
       <c r="L140" t="n">
@@ -36541,17 +36576,17 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 星宇橙色 - MG074CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>195****41158</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L142" t="n">
@@ -36612,17 +36647,17 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 512GB 星宇橙色 - MG074CH/A</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41158</t>
         </is>
       </c>
       <c r="L143" t="n">
@@ -36893,23 +36928,20 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>iPad基础版</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
+          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>6923517323407</t>
+          <t>195****86379</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
-      </c>
-      <c r="M147" t="n">
         <v>1</v>
       </c>
       <c r="N147" t="n">
@@ -37032,20 +37064,23 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>iPad基础版</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>11 英寸 iPad GPS 128GB/蓝色-MD4A4CH/A</t>
+          <t>NO1BOX IPhone 17 Pro Max 蜡笔小新春日部防卫队保护壳 出发啦</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>195****86379</t>
+          <t>6923517323407</t>
         </is>
       </c>
       <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
         <v>1</v>
       </c>
       <c r="N149" t="n">
@@ -37105,12 +37140,12 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127005</t>
         </is>
       </c>
       <c r="L150" t="n">
@@ -37176,12 +37211,12 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>6942297127005</t>
+          <t>6942297127241</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -37242,17 +37277,17 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动保护皮套带笔槽  11 英寸 iPad (A16) 动物派对</t>
+          <t>LIBRATONE小鸟音响 UP 耳机</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>6942297127241</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -37313,17 +37348,17 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L153" t="n">
@@ -37460,12 +37495,12 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
+          <t>RICHIC锐壳 iPad 高清保护膜</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>6942297127012</t>
+          <t>6974623613036</t>
         </is>
       </c>
       <c r="L155" t="n">
@@ -37531,12 +37566,12 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPad 高清保护膜</t>
+          <t>COMMA珂玛 iPad 灵动系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>6974623613036</t>
+          <t>6942297127012</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -41136,17 +41171,17 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6927123810344</t>
         </is>
       </c>
       <c r="L207" t="n">
@@ -41278,17 +41313,17 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
+          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>195****10144</t>
+          <t>6927123810436</t>
         </is>
       </c>
       <c r="L209" t="n">
@@ -41420,17 +41455,17 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 无极 360 度旋转支架保护壳 灰色 iPhone 17</t>
+          <t>AppleCare Services for iPhone 17 - SY7L2CH/A</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>6927123810436</t>
+          <t>195****10144</t>
         </is>
       </c>
       <c r="L211" t="n">
@@ -41491,17 +41526,17 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 二强防静电高清钢化膜 透明</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>6927123810344</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L212" t="n">
@@ -41988,17 +42023,17 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L219" t="n">
@@ -42059,17 +42094,17 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L220" t="n">
@@ -42130,17 +42165,17 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L221" t="n">
@@ -42414,17 +42449,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>6941876245437</t>
+          <t>4894222083820</t>
         </is>
       </c>
       <c r="L225" t="n">
@@ -42485,17 +42520,17 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>UGREEN绿联 USB-C 充电线 1.5m 100W 黑色</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6941876245437</t>
         </is>
       </c>
       <c r="L226" t="n">
@@ -42556,17 +42591,17 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 黑色</t>
+          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>4894222083820</t>
+          <t>6974623613029</t>
         </is>
       </c>
       <c r="L227" t="n">
@@ -42627,17 +42662,17 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 氮化镓三口充电器 65W</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>6974623613029</t>
+          <t>6928288500057</t>
         </is>
       </c>
       <c r="L228" t="n">
@@ -42698,17 +42733,17 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 橙色</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>6928288500057</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L229" t="n">
@@ -42774,12 +42809,12 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L230" t="n">
@@ -42840,17 +42875,17 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L231" t="n">
@@ -43271,18 +43306,15 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>Osmo Pocket 4P 标准套装</t>
+          <t>Osmo 迷你三脚架</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>6937224148321</t>
+          <t>6941565969811</t>
         </is>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
-      </c>
-      <c r="M237" t="n">
         <v>1</v>
       </c>
       <c r="N237" t="n">
@@ -43337,20 +43369,23 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>Pocket</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（小号）</t>
+          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>6937224129559</t>
+          <t>6937224151062</t>
         </is>
       </c>
       <c r="L238" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="n">
         <v>1</v>
       </c>
       <c r="N238" t="n">
@@ -43410,12 +43445,12 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Osmo 迷你三脚架</t>
+          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>6941565969811</t>
+          <t>6937224151062</t>
         </is>
       </c>
       <c r="L239" t="n">
@@ -43473,17 +43508,17 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Pocket</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
+          <t>DJI 无纺布购物袋（小号）</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>6937224151062</t>
+          <t>6937224129559</t>
         </is>
       </c>
       <c r="L240" t="n">
@@ -43614,12 +43649,12 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>DJI Care 随心换 1年版（Osmo Pocket 4P）中国版</t>
+          <t>Osmo Pocket 4P 标准套装</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>6937224151062</t>
+          <t>6937224148321</t>
         </is>
       </c>
       <c r="L242" t="n">
@@ -45455,17 +45490,17 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>FreeClip</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>FreeClip 2 耳夹耳机无线充 摩登黑</t>
+          <t>礼品-定制-音频Freeclip 2配饰-贝母甜心</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>6942103169403</t>
+          <t>A0800888</t>
         </is>
       </c>
       <c r="L268" t="n">
@@ -45526,17 +45561,17 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>FreeClip</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>礼品-定制-音频Freeclip 2配饰-贝母甜心</t>
+          <t>FreeClip 2 耳夹耳机无线充 摩登黑</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>A0800888</t>
+          <t>6942103169403</t>
         </is>
       </c>
       <c r="L269" t="n">
@@ -45957,12 +45992,12 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>6941487218028</t>
+          <t>6941487218011</t>
         </is>
       </c>
       <c r="L275" t="n">
@@ -46028,12 +46063,12 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 白色</t>
+          <t>10000 mah超级快充多协议电源 Max 22.5W SE P0008 黑色</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>6941487218011</t>
+          <t>6941487218028</t>
         </is>
       </c>
       <c r="L276" t="n">
@@ -46875,12 +46910,12 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>6922329936645</t>
+          <t>6922329936577</t>
         </is>
       </c>
       <c r="L288" t="n">
@@ -46946,12 +46981,12 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 橙色</t>
+          <t>VOKAMO沃咔曼 USB-C 60W iPhone 数据传输线 橙色</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>6922329936577</t>
+          <t>6922329936645</t>
         </is>
       </c>
       <c r="L289" t="n">
@@ -47296,17 +47331,17 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>6977503191334</t>
+          <t>6942297146426</t>
         </is>
       </c>
       <c r="L294" t="n">
@@ -47367,17 +47402,17 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
+          <t>SWITCHEASY Apple Watch 系列 Mesh 不锈钢磁扣表带</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>6942297146426</t>
+          <t>6977503191334</t>
         </is>
       </c>
       <c r="L295" t="n">
@@ -47443,12 +47478,12 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>ZGA 明透磁吸 保护壳 透明 iPhone 16e</t>
+          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>6927123805746</t>
+          <t>6927123809881</t>
         </is>
       </c>
       <c r="L296" t="n">
@@ -47585,12 +47620,12 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>ZGA iPhone 系列 裸感鹰眼镜头膜 透明 iPhone 17</t>
+          <t>ZGA 明透磁吸 保护壳 透明 iPhone 16e</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>6927123809881</t>
+          <t>6927123805746</t>
         </is>
       </c>
       <c r="L298" t="n">
@@ -48148,17 +48183,17 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
+          <t>LIBRATONE小鸟音响 UP 耳机</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>6922329934283</t>
+          <t>6975324441119</t>
         </is>
       </c>
       <c r="L306" t="n">
@@ -48219,17 +48254,17 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>LIBRATONE小鸟音响 UP 耳机</t>
+          <t>VOKAMO沃咔曼 iPad Air 魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>6975324441119</t>
+          <t>6922329934283</t>
         </is>
       </c>
       <c r="L307" t="n">
@@ -48645,17 +48680,17 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>6927123810412</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L313" t="n">
@@ -48787,17 +48822,17 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>ZGA iPhone 17 Pro Max 二强防静电高清钢化膜 透明</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6927123810412</t>
         </is>
       </c>
       <c r="L315" t="n">
@@ -53514,17 +53549,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>保护</t>
+          <t>华为Care+</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t xml:space="preserve">仁清 高清原透膜 </t>
+          <t>199元 HUAWEI Care+（一年期） 适用于 Chenzhen 第1代 A款 （华为畅享 90 Pro Max） 12月 不限次 2C 出险收费</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>6937362403306</t>
+          <t>8813044357</t>
         </is>
       </c>
       <c r="L382" t="n">
@@ -53585,17 +53620,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>华为Care+</t>
+          <t>保护</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>199元 HUAWEI Care+（一年期） 适用于 Chenzhen 第1代 A款 （华为畅享 90 Pro Max） 12月 不限次 2C 出险收费</t>
+          <t xml:space="preserve">仁清 高清原透膜 </t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>8813044357</t>
+          <t>6937362403306</t>
         </is>
       </c>
       <c r="L383" t="n">
@@ -54357,17 +54392,17 @@
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41127</t>
         </is>
       </c>
       <c r="L394" t="n">
@@ -54428,17 +54463,17 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 星宇橙色 - MG044CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>195****41127</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L395" t="n">
@@ -54499,17 +54534,17 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>ZGA iPad 流派系列 Y 折 保护皮套</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6927123806750</t>
         </is>
       </c>
       <c r="L396" t="n">
@@ -54570,17 +54605,17 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>ZGA iPad 流派系列 Y 折 保护皮套</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>6927123806750</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L397" t="n">
@@ -54641,17 +54676,17 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
         </is>
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6946333017596</t>
         </is>
       </c>
       <c r="L398" t="n">
@@ -54712,17 +54747,17 @@
       </c>
       <c r="I399" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>SENNHEISER森海塞尔 ACCENTUM 无线蓝牙头戴主动降噪耳机 白色</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4260752330572</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L399" t="n">
@@ -54854,17 +54889,17 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>SENNHEISER森海塞尔 ACCENTUM 无线蓝牙头戴主动降噪耳机 白色</t>
         </is>
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>4260752330572</t>
         </is>
       </c>
       <c r="L401" t="n">
@@ -54925,17 +54960,17 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>HUNTKEY航嘉 USB-C 4合一 多功能扩展坞 黑色</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>6946333017596</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L402" t="n">
@@ -55067,17 +55102,17 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>JBL 杰宝 Soundgear Clips 开放式真无线耳机 深空黑</t>
+          <t>iPhone 17 Pro Max 512GB 银色 - MG064CH/A</t>
         </is>
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>050036415521</t>
+          <t>195****41141</t>
         </is>
       </c>
       <c r="L404" t="n">
@@ -55138,17 +55173,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 银色 - MG064CH/A</t>
+          <t>JBL 杰宝 Soundgear Clips 开放式真无线耳机 深空黑</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>195****41141</t>
+          <t>050036415521</t>
         </is>
       </c>
       <c r="L405" t="n">
@@ -55777,17 +55812,17 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>表带</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
+          <t>ZGA 海洋硅胶表带 Watch 42/44/45/49mm 白色</t>
         </is>
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>6942297146426</t>
+          <t>6927123804718</t>
         </is>
       </c>
       <c r="L414" t="n">
@@ -55919,17 +55954,17 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>表带</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>ZGA 海洋硅胶表带 Watch 42/44/45/49mm 白色</t>
+          <t>COMMA珂玛  盾威系列全屏 Apple Watch 46mm 保护膜 V3</t>
         </is>
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>6927123804718</t>
+          <t>6942297146426</t>
         </is>
       </c>
       <c r="L416" t="n">
@@ -55990,17 +56025,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro 512GB 银色 - MG8W4CH/A</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****28890</t>
         </is>
       </c>
       <c r="L417" t="n">
@@ -56061,17 +56096,17 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 512GB 银色 - MG8W4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>195****28890</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L418" t="n">
@@ -56487,17 +56522,17 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L424" t="n">
@@ -56629,17 +56664,17 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6927123805432</t>
         </is>
       </c>
       <c r="L426" t="n">
@@ -56700,17 +56735,17 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>6927123805432</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L427" t="n">
@@ -56984,17 +57019,17 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 Pro Max 迪士尼莓果草莓熊磁吸保护壳 粉色</t>
+          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>6975749267219</t>
+          <t>6928288555361</t>
         </is>
       </c>
       <c r="L431" t="n">
@@ -57055,17 +57090,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>Applecare+</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
+          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>195****10113</t>
+          <t>6927123810405</t>
         </is>
       </c>
       <c r="L432" t="n">
@@ -57197,17 +57232,17 @@
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>Applecare+</t>
         </is>
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>ZGA iPhone 17 Pro Max 防偷窥防静电二强钢化膜 黑色</t>
+          <t>AppleCare Services for iPhone 17 Pro Max - SY7P2CH/A</t>
         </is>
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>6927123810405</t>
+          <t>195****10113</t>
         </is>
       </c>
       <c r="L434" t="n">
@@ -57268,17 +57303,17 @@
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>IDMIX 大麦 Q10IIISE 10000mAh 27W 磁吸 亿纬锂能电芯移动电源 白色</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>6928288555361</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L435" t="n">
@@ -57339,17 +57374,17 @@
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>RICHIC锐壳 iPhone 17 Pro Max 透明磨砂保护壳 透明</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>6978880670153</t>
         </is>
       </c>
       <c r="L436" t="n">
@@ -57415,12 +57450,12 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>RICHIC锐壳 iPhone 17 Pro Max 透明磨砂保护壳 透明</t>
+          <t>LEMANCHUANGYAN乐漫创衍 iPhone 17 Pro Max 迪士尼莓果草莓熊磁吸保护壳 粉色</t>
         </is>
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>6978880670153</t>
+          <t>6975749267219</t>
         </is>
       </c>
       <c r="L437" t="n">
@@ -57907,17 +57942,17 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>SOUNDCORE声阔 Life Q45 无线蓝牙耳机头戴式降噪耳机</t>
+          <t>iPhone 17 Pro Max 256GB 银色 - MG034CH/A</t>
         </is>
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>6940268897810</t>
+          <t>195****41110</t>
         </is>
       </c>
       <c r="L444" t="n">
@@ -57978,17 +58013,17 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 256GB 银色 - MG034CH/A</t>
+          <t>SOUNDCORE声阔 Life Q45 无线蓝牙耳机头戴式降噪耳机</t>
         </is>
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>195****41110</t>
+          <t>6940268897810</t>
         </is>
       </c>
       <c r="L445" t="n">
@@ -58191,17 +58226,17 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro 512GB 银色 - MG8W4CH/A</t>
         </is>
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****28890</t>
         </is>
       </c>
       <c r="L448" t="n">
@@ -58262,17 +58297,17 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro 512GB 银色 - MG8W4CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>195****28890</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L449" t="n">
@@ -62941,12 +62976,12 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>WATCH GT 7 Pro 46mm 钛色钛合金表壳 绿色氟橡胶表带 松霜绿</t>
+          <t>WATCH GT 7 Pro 46mm 黑色钛合金表壳 黑色氟橡胶表带 碳晶黑</t>
         </is>
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>6942711307624</t>
+          <t>6942711307600</t>
         </is>
       </c>
       <c r="L515" t="n">
@@ -63012,12 +63047,12 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>WATCH GT 7 Pro 46mm 黑色钛合金表壳 黑色氟橡胶表带 碳晶黑</t>
+          <t>WATCH GT 7 Pro 46mm 钛色钛合金表壳 黄色氟橡胶表带  境野黄</t>
         </is>
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>6942711307600</t>
+          <t>6942711307617</t>
         </is>
       </c>
       <c r="L516" t="n">
@@ -63083,12 +63118,12 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>WATCH GT 7 Pro 46mm 黑色钛合金表壳 黑色氟橡胶表带 碳晶黑</t>
+          <t>WATCH GT 7 Pro 46mm 钛色钛合金表壳 绿色氟橡胶表带 松霜绿</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>6942711307600</t>
+          <t>6942711307624</t>
         </is>
       </c>
       <c r="L517" t="n">
@@ -63154,12 +63189,12 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>WATCH GT 7 Pro 46mm 钛色钛合金表壳 黄色氟橡胶表带  境野黄</t>
+          <t>WATCH GT 7 Pro 46mm 黑色钛合金表壳 黑色氟橡胶表带 碳晶黑</t>
         </is>
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>6942711307617</t>
+          <t>6942711307600</t>
         </is>
       </c>
       <c r="L518" t="n">
@@ -63220,17 +63255,17 @@
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>礼品</t>
+          <t>FreeClip</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>礼品-定制-音频Freeclip 2配饰-花点心思</t>
+          <t>FreeClip 2 耳夹耳机无线充 玫瑰金</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>A0800889</t>
+          <t>6942103178726</t>
         </is>
       </c>
       <c r="L519" t="n">
@@ -63291,17 +63326,17 @@
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>FreeClip</t>
+          <t>礼品</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>FreeClip 2 耳夹耳机无线充 玫瑰金</t>
+          <t>礼品-定制-音频Freeclip 2配饰-花点心思</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>6942103178726</t>
+          <t>A0800889</t>
         </is>
       </c>
       <c r="L520" t="n">
@@ -63722,12 +63757,12 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
+          <t>TimeLock Mate 80/80 Pro 3D 康宁高清全屏 钢化膜</t>
         </is>
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>6941402717384</t>
+          <t>6979434900252</t>
         </is>
       </c>
       <c r="L526" t="n">
@@ -63793,12 +63828,12 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>TimeLock Mate 80/80 Pro 3D 康宁高清全屏 钢化膜</t>
+          <t>仁清 UV高清晶钻膜 180GJZ-01G9是（S码）</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>6979434900252</t>
+          <t>6941402717384</t>
         </is>
       </c>
       <c r="L527" t="n">
